--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486828_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486828_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6091</v>
+        <v>3.1954</v>
       </c>
       <c r="E2" t="n">
-        <v>6.452</v>
+        <v>6.6658</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.8428</v>
+        <v>-3.4704</v>
       </c>
       <c r="G2" t="n">
         <v>6.0575</v>
@@ -610,13 +610,13 @@
         <v>1.1585</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1861</v>
+        <v>-0.5998</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1659</v>
+        <v>0.0479</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.0202</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>-2.4554</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. PARRONDO CASTRO</t>
+          <t>P. RODRIGUEZ FAJARDO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4884</v>
+        <v>2.242</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2398</v>
+        <v>2.6152</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2486</v>
+        <v>-0.3731</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6739</v>
+        <v>1.5456</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1653</v>
+        <v>1.5998</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5086000000000001</v>
+        <v>-0.0542</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5787</v>
+        <v>2.8844</v>
       </c>
       <c r="K3" t="n">
-        <v>2.373</v>
+        <v>1.7381</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2057</v>
+        <v>1.1462</v>
       </c>
       <c r="M3" t="n">
-        <v>0.09520000000000001</v>
+        <v>-1.3388</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2077</v>
+        <v>-0.1384</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3029</v>
+        <v>-1.2005</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.0892</v>
+        <v>1.1585</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.8616</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7723</v>
+        <v>1.1585</v>
       </c>
       <c r="S3" t="n">
-        <v>0.734</v>
+        <v>-0.462</v>
       </c>
       <c r="T3" t="n">
-        <v>0.496</v>
+        <v>-0.2692</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2379</v>
+        <v>-0.1928</v>
       </c>
       <c r="V3" t="n">
-        <v>2.1698</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>3.0266</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8568</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ FAJARDO</t>
+          <t>J. PARRONDO CASTRO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6724</v>
+        <v>1.734</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1946</v>
+        <v>1.8331</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5221</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5456</v>
+        <v>2.6739</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5998</v>
+        <v>2.1653</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0542</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8844</v>
+        <v>2.5787</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7381</v>
+        <v>2.373</v>
       </c>
       <c r="L4" t="n">
-        <v>1.1462</v>
+        <v>0.2057</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3388</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1384</v>
+        <v>-0.2077</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2005</v>
+        <v>0.3029</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1585</v>
+        <v>-3.0892</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-3.8616</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0316</v>
+        <v>-0.0204</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6898</v>
+        <v>0.0893</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3418</v>
+        <v>-0.1097</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2.1698</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.0266</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.8568</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MORENO CASTRO</t>
+          <t>M. DIAZ FELST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3373</v>
+        <v>1.1498</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1794</v>
+        <v>2.2379</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5167</v>
+        <v>-1.0881</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3727</v>
+        <v>2.2575</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4412</v>
+        <v>0.7858000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8138</v>
+        <v>1.4717</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.317</v>
+        <v>2.4382</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3725</v>
+        <v>1.1314</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6895</v>
+        <v>1.3067</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0557</v>
+        <v>-0.1806</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0687</v>
+        <v>-0.3456</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1244</v>
+        <v>0.165</v>
       </c>
       <c r="P5" t="n">
         <v>0.7723</v>
@@ -844,28 +844,28 @@
         <v>0.7723</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3752</v>
+        <v>-0.7376</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1377</v>
+        <v>-0.2003</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5129</v>
+        <v>-0.5374</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3129</v>
+        <v>-1.1424</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.3129</v>
+        <v>-1.1424</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. FLORES LUCAS</t>
+          <t>J. MORENO CASTRO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.517</v>
+        <v>1.023</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0345</v>
+        <v>-0.593</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5515</v>
+        <v>1.616</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0205</v>
+        <v>-0.3727</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1174</v>
+        <v>0.4412</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1379</v>
+        <v>-0.8138</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0207</v>
+        <v>-0.317</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0207</v>
+        <v>0.3725</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.6895</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0002</v>
+        <v>-0.0557</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1381</v>
+        <v>0.0687</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1379</v>
+        <v>-0.1244</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.7723</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.7723</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.16</v>
+        <v>-0.6896</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0552</v>
+        <v>-0.276</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1048</v>
+        <v>-0.4136</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6565</v>
+        <v>1.3129</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6565</v>
+        <v>1.3129</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. DIAZ FELST</t>
+          <t>D. FLORES LUCAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2988</v>
+        <v>0.6701</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6104</v>
+        <v>0.0689</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3116</v>
+        <v>0.6012</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2575</v>
+        <v>0.0205</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7858000000000001</v>
+        <v>-0.1174</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4717</v>
+        <v>0.1379</v>
       </c>
       <c r="J7" t="n">
-        <v>2.4382</v>
+        <v>0.0207</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1314</v>
+        <v>0.0207</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3067</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1806</v>
+        <v>-0.0002</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3456</v>
+        <v>-0.1381</v>
       </c>
       <c r="O7" t="n">
-        <v>0.165</v>
+        <v>0.1379</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7723</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7723</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.5886</v>
+        <v>-0.0069</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8277</v>
+        <v>0.0482</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7609</v>
+        <v>-0.0551</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.1424</v>
+        <v>0.6565</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1424</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. GONZALEZ GRANDE</t>
+          <t>A. GOMEZ PEÑA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2163</v>
+        <v>0.4022</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1103</v>
+        <v>-1.3897</v>
       </c>
       <c r="F8" t="n">
-        <v>0.106</v>
+        <v>1.792</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4756</v>
+        <v>0.2637</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3309</v>
+        <v>-0.5592</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1447</v>
+        <v>0.8229</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3311</v>
+        <v>-0.5207000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3311</v>
+        <v>-0.4892</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.0315</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1445</v>
+        <v>0.7845</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0002</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1447</v>
+        <v>0.8544</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3862</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3862</v>
+        <v>1.3515</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6454</v>
+        <v>-0.51</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2207</v>
+        <v>-0.1659</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4247</v>
+        <v>-0.3441</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. GONZALEZ-MONJE PEREZ</t>
+          <t>R. GONZALEZ GRANDE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1348</v>
+        <v>0.3446</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6291</v>
+        <v>0.2138</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4943</v>
+        <v>0.1308</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1528</v>
+        <v>0.4756</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3655</v>
+        <v>0.3309</v>
       </c>
       <c r="I9" t="n">
-        <v>2.5183</v>
+        <v>0.1447</v>
       </c>
       <c r="J9" t="n">
-        <v>0.657</v>
+        <v>0.3311</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2962</v>
+        <v>0.3311</v>
       </c>
       <c r="L9" t="n">
-        <v>1.9532</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4958</v>
+        <v>0.1445</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0693</v>
+        <v>-0.0002</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5651</v>
+        <v>0.1447</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5792</v>
+        <v>0.3862</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0.3862</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7889</v>
+        <v>-0.5171</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9375</v>
+        <v>-0.1173</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1486</v>
+        <v>-0.3998</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. GOMEZ PEÑA</t>
+          <t>M. GONZALEZ-MONJE PEREZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2624</v>
+        <v>-0.585</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3275</v>
+        <v>0.0086</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0651</v>
+        <v>-0.5937</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2637</v>
+        <v>1.1528</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5592</v>
+        <v>-1.3655</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8229</v>
+        <v>2.5183</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5207000000000001</v>
+        <v>0.657</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4892</v>
+        <v>-1.2962</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0315</v>
+        <v>1.9532</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7845</v>
+        <v>0.4958</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.0693</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8544</v>
+        <v>0.5651</v>
       </c>
       <c r="P10" t="n">
         <v>-0.5792</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3515</v>
+        <v>0.3862</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1745</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1036</v>
+        <v>0.317</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0709</v>
+        <v>-0.2479</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2277</v>
+        <v>-1.2277</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5249</v>
+        <v>-2.4504</v>
       </c>
       <c r="E11" t="n">
         <v>-1.395</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1299</v>
+        <v>-1.0554</v>
       </c>
       <c r="G11" t="n">
         <v>-1.8353</v>
@@ -1312,13 +1312,13 @@
         <v>0.3862</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4193</v>
+        <v>-0.3448</v>
       </c>
       <c r="T11" t="n">
         <v>-0.1932</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2261</v>
+        <v>-0.1516</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6565</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6634</v>
+        <v>-3.1185</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.0118</v>
+        <v>-2.2186</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6516</v>
+        <v>-0.8999</v>
       </c>
       <c r="G12" t="n">
         <v>-4.6278</v>
@@ -1390,13 +1390,13 @@
         <v>0.9654</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1655</v>
+        <v>-0.2896</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2204</v>
+        <v>0.0135</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0548</v>
+        <v>-0.3031</v>
       </c>
       <c r="V12" t="n">
         <v>1.7989</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.1157</v>
+        <v>-3.3474</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.4157</v>
+        <v>-0.6226</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.7</v>
+        <v>-2.7248</v>
       </c>
       <c r="G13" t="n">
         <v>-1.7158</v>
@@ -1468,13 +1468,13 @@
         <v>0.5792</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0717</v>
+        <v>-0.3034</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2204</v>
+        <v>0.0135</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2921</v>
+        <v>-0.3169</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9421</v>
@@ -1501,22 +1501,22 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7077000000000004</v>
+        <v>1.259800000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>6.872300000000001</v>
+        <v>7.4244</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.1644</v>
+        <v>-6.1645</v>
       </c>
       <c r="G14" t="n">
         <v>5.895500000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>7.240600000000001</v>
+        <v>7.240599999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.345100000000001</v>
+        <v>-1.3451</v>
       </c>
       <c r="J14" t="n">
         <v>11.8028</v>
@@ -1537,22 +1537,22 @@
         <v>-4.5219</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9652000000000002</v>
+        <v>-0.9651999999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-9.654000000000002</v>
+        <v>-9.654</v>
       </c>
       <c r="R14" t="n">
         <v>8.688599999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.964</v>
+        <v>-4.4121</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2441</v>
+        <v>-0.6925000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.7199</v>
+        <v>-3.7197</v>
       </c>
       <c r="V14" t="n">
         <v>0.7416999999999997</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.7177</v>
+        <v>4.137</v>
       </c>
       <c r="E15" t="n">
-        <v>4.7517</v>
+        <v>4.9585</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0339</v>
+        <v>-0.8216</v>
       </c>
       <c r="G15" t="n">
         <v>1.3096</v>
@@ -1624,13 +1624,13 @@
         <v>0.7723</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4082</v>
+        <v>0.8274</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2479</v>
+        <v>0.4547</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1603</v>
+        <v>0.3727</v>
       </c>
       <c r="V15" t="n">
         <v>1.2277</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4044</v>
+        <v>3.9642</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3845</v>
+        <v>3.005</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0199</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>0.4114</v>
@@ -1702,13 +1702,13 @@
         <v>0.9654</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1435</v>
+        <v>0.7032</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2761</v>
+        <v>0.3444</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4196</v>
+        <v>0.3589</v>
       </c>
       <c r="V16" t="n">
         <v>1.8842</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Í. MATEO CASTAÑO</t>
+          <t>A. FORTES SILVA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4711</v>
+        <v>0.7304</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9492</v>
+        <v>2.1661</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4781</v>
+        <v>-1.4357</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.3407</v>
+        <v>-1.1152</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8004</v>
+        <v>0.1598</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5403</v>
+        <v>-1.2751</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4019</v>
+        <v>1.9345</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1655</v>
+        <v>1.6089</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5674</v>
+        <v>0.3255</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9388</v>
+        <v>-3.0497</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9659</v>
+        <v>-1.4491</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0271</v>
+        <v>-1.6006</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3515</v>
+        <v>0.3862</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R17" t="n">
         <v>1.3515</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6879</v>
+        <v>0.317</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3511</v>
+        <v>0.0546</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3368</v>
+        <v>0.2624</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2277</v>
+        <v>1.1424</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.1424</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. SANTOLARIA MARTIN</t>
+          <t>R. TERRATS MADRID</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4255</v>
+        <v>-0.1096</v>
       </c>
       <c r="E18" t="n">
-        <v>2.8122</v>
+        <v>0.9356</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.3868</v>
+        <v>-1.0452</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1803</v>
+        <v>-0.0237</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1791</v>
+        <v>0.4895</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3595</v>
+        <v>-0.5132</v>
       </c>
       <c r="J18" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.5153</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0414</v>
+        <v>1.7315</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0407</v>
+        <v>-1.2162</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2624</v>
+        <v>-0.539</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1377</v>
+        <v>-1.242</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4002</v>
+        <v>0.703</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3862</v>
+        <v>1.1585</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3862</v>
+        <v>1.1585</v>
       </c>
       <c r="S18" t="n">
-        <v>2.675</v>
+        <v>0.2689</v>
       </c>
       <c r="T18" t="n">
-        <v>2.7301</v>
+        <v>0.4203</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0551</v>
+        <v>-0.1513</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.4554</v>
+        <v>-1.5133</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.4554</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. TERRATS MADRID</t>
+          <t>G. CAMPOS MARCOS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3839</v>
+        <v>-0.2359</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6253</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0092</v>
+        <v>0.4481</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0237</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4895</v>
+        <v>0.4551</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5132</v>
+        <v>-0.4634</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5153</v>
+        <v>-0.5667</v>
       </c>
       <c r="K19" t="n">
-        <v>1.7315</v>
+        <v>0.0414</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2162</v>
+        <v>-0.6081</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.539</v>
+        <v>0.5583</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.242</v>
+        <v>0.4137</v>
       </c>
       <c r="O19" t="n">
-        <v>0.703</v>
+        <v>0.1447</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1585</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1585</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0054</v>
+        <v>-0.2276</v>
       </c>
       <c r="T19" t="n">
-        <v>0.11</v>
+        <v>-0.1173</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1154</v>
+        <v>-0.1102</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.5133</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.5133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. FORTES SILVA</t>
+          <t>A. MARÍN REYES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4087</v>
+        <v>-0.5178</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3387</v>
+        <v>0.3964</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7475</v>
+        <v>-0.9142</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1152</v>
+        <v>-1.9289</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1598</v>
+        <v>-1.8069</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2751</v>
+        <v>-0.1221</v>
       </c>
       <c r="J20" t="n">
-        <v>1.9345</v>
+        <v>0.0239</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6089</v>
+        <v>-1.3235</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3255</v>
+        <v>1.3474</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.0497</v>
+        <v>-1.9528</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4491</v>
+        <v>-0.4833</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.6006</v>
+        <v>-1.4695</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3862</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3515</v>
+        <v>1.1585</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8221000000000001</v>
+        <v>0.0136</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7728</v>
+        <v>-0.1521</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0493</v>
+        <v>0.1658</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1424</v>
+        <v>2.1698</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1424</v>
+        <v>2.4554</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. CAMPOS MARCOS</t>
+          <t>Í. MATEO CASTAÑO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4387</v>
+        <v>-0.5342</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7874</v>
+        <v>0.0184</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3488</v>
+        <v>-0.5526</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-1.3407</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4551</v>
+        <v>-0.8004</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4634</v>
+        <v>-0.5403</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5667</v>
+        <v>-0.4019</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0414</v>
+        <v>0.1655</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6081</v>
+        <v>-0.5674</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5583</v>
+        <v>-0.9388</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4137</v>
+        <v>-0.9659</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1447</v>
+        <v>0.0271</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.3515</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.3515</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4303</v>
+        <v>0.6826</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2207</v>
+        <v>0.4203</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2096</v>
+        <v>0.2624</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0358</v>
+        <v>-0.6925</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3168</v>
+        <v>-1.7997</v>
       </c>
       <c r="F22" t="n">
-        <v>1.281</v>
+        <v>1.1071</v>
       </c>
       <c r="G22" t="n">
         <v>0.3168</v>
@@ -2170,13 +2170,13 @@
         <v>0.5792</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0223</v>
+        <v>0.3655</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2759</v>
+        <v>0.2412</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2982</v>
+        <v>0.1243</v>
       </c>
       <c r="V22" t="n">
         <v>0.9421</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. MARÍN REYES</t>
+          <t>J. SANTOLARIA MARTIN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4749</v>
+        <v>-1.1051</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.2242</v>
+        <v>1.1575</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2507</v>
+        <v>-2.2626</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.9289</v>
+        <v>-0.1803</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.8069</v>
+        <v>0.1791</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1221</v>
+        <v>-0.3595</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0239</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.3235</v>
+        <v>0.0414</v>
       </c>
       <c r="L23" t="n">
-        <v>1.3474</v>
+        <v>0.0407</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.9528</v>
+        <v>-0.2624</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4833</v>
+        <v>0.1377</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.4695</v>
+        <v>-0.4002</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.7723</v>
+        <v>0.3862</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1585</v>
+        <v>0.3862</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9434</v>
+        <v>1.1444</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7727000000000001</v>
+        <v>1.0754</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1708</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>2.1698</v>
+        <v>-2.4554</v>
       </c>
       <c r="W23" t="n">
-        <v>2.4554</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2856</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. BALLESPIN DE LA PEÑA</t>
+          <t>I. IBAÑEZ ZAMALLOA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.29</v>
+        <v>-2.6823</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.2589</v>
+        <v>-0.7996</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0311</v>
+        <v>-1.8827</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.9118000000000001</v>
+        <v>-2.4243</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.5312</v>
+        <v>-1.0273</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6194</v>
+        <v>-1.397</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6421</v>
+        <v>0.6254</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.5653</v>
+        <v>0.2838</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.07679999999999999</v>
+        <v>0.3416</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2697</v>
+        <v>-3.0497</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.9659</v>
+        <v>-1.3112</v>
       </c>
       <c r="O24" t="n">
-        <v>0.6962</v>
+        <v>-1.7385</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.1585</v>
+        <v>0.1931</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R24" t="n">
-        <v>0.7723</v>
+        <v>1.1585</v>
       </c>
       <c r="S24" t="n">
-        <v>1.3788</v>
+        <v>0.8618</v>
       </c>
       <c r="T24" t="n">
-        <v>1.627</v>
+        <v>0.2821</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2481</v>
+        <v>0.5797</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.5985</v>
+        <v>-1.3129</v>
       </c>
       <c r="W24" t="n">
-        <v>-1.3129</v>
+        <v>-0.7417</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.2856</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>I. IBAÑEZ ZAMALLOA</t>
+          <t>P. BALLESPIN DE LA PEÑA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.6946</v>
+        <v>-2.9724</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.1098</v>
+        <v>-3.1897</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.5848</v>
+        <v>0.2172</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.4243</v>
+        <v>-0.9118000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.0273</v>
+        <v>-1.5312</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.397</v>
+        <v>0.6194</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6254</v>
+        <v>-0.6421</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2838</v>
+        <v>-0.5653</v>
       </c>
       <c r="L25" t="n">
-        <v>0.3416</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.0497</v>
+        <v>-0.2697</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.3112</v>
+        <v>-0.9659</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.7385</v>
+        <v>0.6962</v>
       </c>
       <c r="P25" t="n">
-        <v>0.1931</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R25" t="n">
-        <v>1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="S25" t="n">
-        <v>0.8496</v>
+        <v>0.6964</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0281</v>
+        <v>0.6962</v>
       </c>
       <c r="U25" t="n">
-        <v>0.8777</v>
+        <v>0.0002</v>
       </c>
       <c r="V25" t="n">
+        <v>-1.5985</v>
+      </c>
+      <c r="W25" t="n">
         <v>-1.3129</v>
       </c>
-      <c r="W25" t="n">
-        <v>-0.7417</v>
-      </c>
       <c r="X25" t="n">
-        <v>-0.5712</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.7079000000000009</v>
+        <v>-0.01820000000000288</v>
       </c>
       <c r="E26" t="n">
-        <v>6.1645</v>
+        <v>6.164500000000002</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.872400000000001</v>
+        <v>-6.183</v>
       </c>
       <c r="G26" t="n">
         <v>-5.8955</v>
@@ -2461,43 +2461,43 @@
         <v>1.3851</v>
       </c>
       <c r="L26" t="n">
-        <v>4.521899999999999</v>
+        <v>4.5219</v>
       </c>
       <c r="M26" t="n">
         <v>-11.8026</v>
       </c>
       <c r="N26" t="n">
-        <v>-8.625999999999999</v>
+        <v>-8.626000000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>-3.1768</v>
+        <v>-3.176799999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>0.9654999999999998</v>
+        <v>0.9654999999999996</v>
       </c>
       <c r="Q26" t="n">
-        <v>-8.688600000000001</v>
+        <v>-8.688599999999999</v>
       </c>
       <c r="R26" t="n">
-        <v>9.6539</v>
+        <v>9.653899999999998</v>
       </c>
       <c r="S26" t="n">
-        <v>4.964099999999999</v>
+        <v>5.6532</v>
       </c>
       <c r="T26" t="n">
-        <v>3.719800000000001</v>
+        <v>3.7198</v>
       </c>
       <c r="U26" t="n">
-        <v>1.2443</v>
+        <v>1.9339</v>
       </c>
       <c r="V26" t="n">
         <v>-0.7415999999999996</v>
       </c>
       <c r="W26" t="n">
-        <v>5.2263</v>
+        <v>5.226300000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-5.967899999999999</v>
+        <v>-5.9679</v>
       </c>
     </row>
   </sheetData>
